--- a/Data/Tables/__tables__.xlsx
+++ b/Data/Tables/__tables__.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangyang/Documents/IAAAProject/MiniTemplate/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangyang/Documents/Deliverables/AdPlayerDemo/Data/Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19855688-E494-D34E-8C6F-D97CA6602AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CDBE7A-5619-E74D-A01D-0F32AAC3C5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12120" yWindow="-13380" windowWidth="29280" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5980" yWindow="-15640" windowWidth="29260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -103,40 +103,31 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>TbMonster</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>TbSample</t>
   </si>
   <si>
     <t>MonsterConfig</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>monsters.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GridTileElements</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>##</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbGridTile</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GridTileConfig.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameConfigs/CardElements.xlsx</t>
+  </si>
+  <si>
+    <t>TbCardElements</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card.CardElement</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>id+level</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -148,22 +139,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -171,7 +153,12 @@
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -184,7 +171,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -205,20 +191,28 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="好" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -231,6 +225,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -277,73 +288,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -355,23 +306,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -381,23 +332,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -405,26 +356,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -459,17 +407,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -497,7 +445,7 @@
     <col min="2" max="2" width="20.33203125" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -593,7 +541,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>27</v>
@@ -613,24 +561,23 @@
     </row>
     <row r="5" spans="1:11">
       <c r="B5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>